--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486271_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486271_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.3586</v>
+        <v>5.2643</v>
       </c>
       <c r="E2" t="n">
-        <v>3.8353</v>
+        <v>3.5252</v>
       </c>
       <c r="F2" t="n">
-        <v>1.5233</v>
+        <v>1.7391</v>
       </c>
       <c r="G2" t="n">
         <v>4.9701</v>
@@ -610,13 +610,13 @@
         <v>3.2626</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.2417</v>
+        <v>-1.336</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.9673</v>
+        <v>-1.2774</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2744</v>
+        <v>-0.0586</v>
       </c>
       <c r="V2" t="n">
         <v>0.7602</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.3041</v>
+        <v>5.022</v>
       </c>
       <c r="E3" t="n">
-        <v>3.0926</v>
+        <v>3.2729</v>
       </c>
       <c r="F3" t="n">
-        <v>2.2115</v>
+        <v>1.7492</v>
       </c>
       <c r="G3" t="n">
         <v>4.0184</v>
@@ -688,13 +688,13 @@
         <v>2.1751</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.5414</v>
+        <v>-0.8235</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.0959</v>
+        <v>-0.9157</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5546</v>
+        <v>0.0922</v>
       </c>
       <c r="V3" t="n">
         <v>0.7395</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.5679</v>
+        <v>4.0439</v>
       </c>
       <c r="E4" t="n">
-        <v>1.6814</v>
+        <v>1.8184</v>
       </c>
       <c r="F4" t="n">
-        <v>1.8864</v>
+        <v>2.2255</v>
       </c>
       <c r="G4" t="n">
         <v>1.0884</v>
@@ -766,13 +766,13 @@
         <v>2.8276</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.651</v>
+        <v>-1.175</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.3699</v>
+        <v>-1.2329</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2811</v>
+        <v>0.058</v>
       </c>
       <c r="V4" t="n">
         <v>1.5204</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.0849</v>
+        <v>3.8016</v>
       </c>
       <c r="E5" t="n">
-        <v>1.4643</v>
+        <v>1.6878</v>
       </c>
       <c r="F5" t="n">
-        <v>1.6207</v>
+        <v>2.1138</v>
       </c>
       <c r="G5" t="n">
         <v>1.6827</v>
@@ -844,13 +844,13 @@
         <v>3.0451</v>
       </c>
       <c r="S5" t="n">
-        <v>-2.5553</v>
+        <v>-1.8386</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.0959</v>
+        <v>-0.8724</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.4593</v>
+        <v>-0.9661999999999999</v>
       </c>
       <c r="V5" t="n">
         <v>1.13</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.9343</v>
+        <v>2.5414</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2959</v>
+        <v>0.0646</v>
       </c>
       <c r="F6" t="n">
-        <v>2.2303</v>
+        <v>2.4769</v>
       </c>
       <c r="G6" t="n">
         <v>2.08</v>
@@ -922,13 +922,13 @@
         <v>2.6101</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.4507</v>
+        <v>-0.8436</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.3014</v>
+        <v>-0.9409</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1493</v>
+        <v>0.0973</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.6184</v>
+        <v>1.1891</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.0328</v>
+        <v>-2.784</v>
       </c>
       <c r="F7" t="n">
-        <v>4.6512</v>
+        <v>3.9731</v>
       </c>
       <c r="G7" t="n">
         <v>1.0042</v>
@@ -1000,13 +1000,13 @@
         <v>3.0451</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7893</v>
+        <v>0.3599</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.0959</v>
+        <v>-0.8472</v>
       </c>
       <c r="U7" t="n">
-        <v>1.8852</v>
+        <v>1.2071</v>
       </c>
       <c r="V7" t="n">
         <v>1.13</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>B. VIDARTE CANO</t>
+          <t>D. STOLBETSKIY</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.4767</v>
+        <v>-1.3694</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0182</v>
+        <v>0.4377</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.495</v>
+        <v>-1.807</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1003</v>
+        <v>0.0134</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.0487</v>
+        <v>0.3194</v>
       </c>
       <c r="I8" t="n">
-        <v>0.149</v>
+        <v>-0.306</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0182</v>
+        <v>0.4629</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0182</v>
+        <v>0.3864</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>0.0765</v>
       </c>
       <c r="M8" t="n">
-        <v>0.082</v>
+        <v>-0.4495</v>
       </c>
       <c r="N8" t="n">
         <v>-0.067</v>
       </c>
       <c r="O8" t="n">
-        <v>0.149</v>
+        <v>-0.3825</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>0.435</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>0.435</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.447</v>
+        <v>-0.1229</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>-0.0252</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.447</v>
+        <v>-0.09760000000000001</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.13</v>
+        <v>-1.695</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.13</v>
+        <v>-1.695</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. STOLBETSKIY</t>
+          <t>B. VIDARTE CANO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.512</v>
+        <v>-1.4767</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3259</v>
+        <v>0.0182</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.8379</v>
+        <v>-1.495</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0134</v>
+        <v>0.1003</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3194</v>
+        <v>-0.0487</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.306</v>
+        <v>0.149</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4629</v>
+        <v>0.0182</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3864</v>
+        <v>0.0182</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0765</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.4495</v>
+        <v>0.082</v>
       </c>
       <c r="N9" t="n">
         <v>-0.067</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.3825</v>
+        <v>0.149</v>
       </c>
       <c r="P9" t="n">
-        <v>0.435</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.435</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2655</v>
+        <v>-0.447</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.137</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1285</v>
+        <v>-0.447</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.695</v>
+        <v>-1.13</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.695</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.7388</v>
+        <v>-2.0402</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.2304</v>
+        <v>-4.1619</v>
       </c>
       <c r="F10" t="n">
-        <v>2.4916</v>
+        <v>2.1217</v>
       </c>
       <c r="G10" t="n">
         <v>-1.3155</v>
@@ -1234,13 +1234,13 @@
         <v>1.7401</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8583</v>
+        <v>-1.1596</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.0274</v>
+        <v>-0.9589</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1692</v>
+        <v>-0.2007</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.5429</v>
+        <v>-6.6932</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.8229</v>
+        <v>-7.1581</v>
       </c>
       <c r="F11" t="n">
-        <v>0.28</v>
+        <v>0.4649</v>
       </c>
       <c r="G11" t="n">
         <v>-3.4738</v>
@@ -1312,13 +1312,13 @@
         <v>1.5225</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.5242</v>
+        <v>-1.6746</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.008399999999999999</v>
+        <v>-0.3437</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.5158</v>
+        <v>-1.3309</v>
       </c>
       <c r="V11" t="n">
         <v>0.1952</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>9.597799999999999</v>
+        <v>10.2828</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.964300000000001</v>
+        <v>-3.279199999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>13.5621</v>
+        <v>13.5622</v>
       </c>
       <c r="G12" t="n">
         <v>10.1682</v>
@@ -1390,10 +1390,10 @@
         <v>20.6632</v>
       </c>
       <c r="S12" t="n">
-        <v>-9.745800000000001</v>
+        <v>-9.0609</v>
       </c>
       <c r="T12" t="n">
-        <v>-8.0991</v>
+        <v>-7.414300000000001</v>
       </c>
       <c r="U12" t="n">
         <v>-1.6464</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>D. POIRIER</t>
+          <t>P. KRUTOUS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.4715</v>
+        <v>2.8073</v>
       </c>
       <c r="E13" t="n">
-        <v>2.3482</v>
+        <v>3.0496</v>
       </c>
       <c r="F13" t="n">
-        <v>1.1233</v>
+        <v>-0.2422</v>
       </c>
       <c r="G13" t="n">
-        <v>2.5639</v>
+        <v>0.8</v>
       </c>
       <c r="H13" t="n">
-        <v>0.2466</v>
+        <v>-0.6176</v>
       </c>
       <c r="I13" t="n">
-        <v>2.3173</v>
+        <v>1.4176</v>
       </c>
       <c r="J13" t="n">
-        <v>2.9186</v>
+        <v>2.8681</v>
       </c>
       <c r="K13" t="n">
-        <v>1.1775</v>
+        <v>1.6242</v>
       </c>
       <c r="L13" t="n">
-        <v>1.7412</v>
+        <v>1.2439</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.3548</v>
+        <v>-2.0681</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.9308999999999999</v>
+        <v>-2.2418</v>
       </c>
       <c r="O13" t="n">
-        <v>0.5760999999999999</v>
+        <v>0.1737</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.7401</v>
+        <v>1.9576</v>
       </c>
       <c r="Q13" t="n">
-        <v>-3.2626</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5225</v>
+        <v>1.9576</v>
       </c>
       <c r="S13" t="n">
-        <v>2.2779</v>
+        <v>1.1798</v>
       </c>
       <c r="T13" t="n">
-        <v>1.5622</v>
+        <v>0.1815</v>
       </c>
       <c r="U13" t="n">
-        <v>0.7157</v>
+        <v>0.9983</v>
       </c>
       <c r="V13" t="n">
-        <v>0.3698</v>
+        <v>-1.13</v>
       </c>
       <c r="W13" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.7602</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>I. CRUZ UCEDA</t>
+          <t>D. POIRIER</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.2984</v>
+        <v>2.5659</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9293</v>
+        <v>1.5659</v>
       </c>
       <c r="F14" t="n">
-        <v>2.3692</v>
+        <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.1434</v>
+        <v>2.5639</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.4933</v>
+        <v>0.2466</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3498</v>
+        <v>2.3173</v>
       </c>
       <c r="J14" t="n">
-        <v>1.0426</v>
+        <v>2.9186</v>
       </c>
       <c r="K14" t="n">
-        <v>0.484</v>
+        <v>1.1775</v>
       </c>
       <c r="L14" t="n">
-        <v>0.5587</v>
+        <v>1.7412</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.1861</v>
+        <v>-0.3548</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.9773</v>
+        <v>-0.9308999999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.2088</v>
+        <v>0.5760999999999999</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.5225</v>
+        <v>-1.7401</v>
       </c>
       <c r="Q14" t="n">
         <v>-3.2626</v>
       </c>
       <c r="R14" t="n">
-        <v>1.7401</v>
+        <v>1.5225</v>
       </c>
       <c r="S14" t="n">
-        <v>4.0949</v>
+        <v>1.3723</v>
       </c>
       <c r="T14" t="n">
-        <v>0.8893</v>
+        <v>0.7799</v>
       </c>
       <c r="U14" t="n">
-        <v>3.2056</v>
+        <v>0.5924</v>
       </c>
       <c r="V14" t="n">
-        <v>1.8695</v>
+        <v>0.3698</v>
       </c>
       <c r="W14" t="n">
-        <v>2.2599</v>
+        <v>1.13</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.3904</v>
+        <v>-0.7602</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P. KRUTOUS</t>
+          <t>I. CRUZ UCEDA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.6243</v>
+        <v>1.6916</v>
       </c>
       <c r="E15" t="n">
-        <v>2.2673</v>
+        <v>0.3705</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.6429</v>
+        <v>1.3212</v>
       </c>
       <c r="G15" t="n">
-        <v>0.8</v>
+        <v>-1.1434</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.6176</v>
+        <v>-1.4933</v>
       </c>
       <c r="I15" t="n">
-        <v>1.4176</v>
+        <v>0.3498</v>
       </c>
       <c r="J15" t="n">
-        <v>2.8681</v>
+        <v>1.0426</v>
       </c>
       <c r="K15" t="n">
-        <v>1.6242</v>
+        <v>0.484</v>
       </c>
       <c r="L15" t="n">
-        <v>1.2439</v>
+        <v>0.5587</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.0681</v>
+        <v>-2.1861</v>
       </c>
       <c r="N15" t="n">
-        <v>-2.2418</v>
+        <v>-1.9773</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1737</v>
+        <v>-0.2088</v>
       </c>
       <c r="P15" t="n">
-        <v>1.9576</v>
+        <v>-1.5225</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-3.2626</v>
       </c>
       <c r="R15" t="n">
-        <v>1.9576</v>
+        <v>1.7401</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.0032</v>
+        <v>2.4881</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6008</v>
+        <v>0.3305</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5976</v>
+        <v>2.1576</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.13</v>
+        <v>1.8695</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>2.2599</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.13</v>
+        <v>-0.3904</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. GARCIA SANCHEZ</t>
+          <t>J. GODSPOWER JOHNSON</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,58 +1657,58 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1713</v>
+        <v>-0.3825</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.0699</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>1.8986</v>
+        <v>-0.3825</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2379</v>
+        <v>-0.3825</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.9033</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>1.1411</v>
+        <v>-0.3825</v>
       </c>
       <c r="J16" t="n">
-        <v>1.129</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.1365</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1.2655</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.8911</v>
+        <v>-0.3825</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.7668</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1243</v>
+        <v>-0.3825</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.7401</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.2626</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5225</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>1.3309</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>0.06370000000000001</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.2672</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. STILMA</t>
+          <t>S. PENO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2889</v>
+        <v>-0.515</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.2976</v>
+        <v>0.0209</v>
       </c>
       <c r="F17" t="n">
-        <v>2.0088</v>
+        <v>-0.5359</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.017</v>
+        <v>-1.1984</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.213</v>
+        <v>-1.7578</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.8041</v>
+        <v>0.5594</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.8783</v>
+        <v>-0.7975</v>
       </c>
       <c r="K17" t="n">
-        <v>0.2039</v>
+        <v>-1.1434</v>
       </c>
       <c r="L17" t="n">
-        <v>-2.0822</v>
+        <v>0.3459</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.1388</v>
+        <v>-0.4009</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.4169</v>
+        <v>-0.6143999999999999</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2781</v>
+        <v>0.2136</v>
       </c>
       <c r="P17" t="n">
-        <v>0.6525</v>
+        <v>1.0875</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.7401</v>
+        <v>1.0875</v>
       </c>
       <c r="S17" t="n">
-        <v>1.0756</v>
+        <v>0.7258</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6682</v>
+        <v>0.8184</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4075</v>
+        <v>-0.0925</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. GODSPOWER JOHNSON</t>
+          <t>M. STILMA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3825</v>
+        <v>-0.5933</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>-2.6329</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.3825</v>
+        <v>2.0396</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.3825</v>
+        <v>-2.017</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>-0.213</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.3825</v>
+        <v>-1.8041</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>-1.8783</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>0.2039</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>-2.0822</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.3825</v>
+        <v>-0.1388</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>-0.4169</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.3825</v>
+        <v>0.2781</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>0.6525</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.7401</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>0.7712</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>0.3329</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>0.4383</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. PENO</t>
+          <t>J. GARCIA SANCHEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.9736</v>
+        <v>-0.6877</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.3144</v>
+        <v>-2.7405</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.6592</v>
+        <v>2.0527</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.1984</v>
+        <v>0.2379</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.7578</v>
+        <v>-0.9033</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5594</v>
+        <v>1.1411</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.7975</v>
+        <v>1.129</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.1434</v>
+        <v>-0.1365</v>
       </c>
       <c r="L19" t="n">
-        <v>0.3459</v>
+        <v>1.2655</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.4009</v>
+        <v>-0.8911</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.6143999999999999</v>
+        <v>-0.7668</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2136</v>
+        <v>-0.1243</v>
       </c>
       <c r="P19" t="n">
-        <v>1.0875</v>
+        <v>-1.7401</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-3.2626</v>
       </c>
       <c r="R19" t="n">
-        <v>1.0875</v>
+        <v>1.5225</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2673</v>
+        <v>0.8145</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4831</v>
+        <v>-0.6068</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2158</v>
+        <v>1.4213</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.0884</v>
+        <v>-1.6549</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.078</v>
+        <v>-2.8603</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9896</v>
+        <v>1.2053</v>
       </c>
       <c r="G20" t="n">
         <v>-3.4674</v>
@@ -2014,13 +2014,13 @@
         <v>1.0875</v>
       </c>
       <c r="S20" t="n">
-        <v>1.2915</v>
+        <v>0.7249</v>
       </c>
       <c r="T20" t="n">
-        <v>0.7367</v>
+        <v>-0.0457</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5548</v>
+        <v>0.7706</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.3262</v>
+        <v>-2.2066</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.692</v>
+        <v>-1.3568</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.6341</v>
+        <v>-0.8499</v>
       </c>
       <c r="G21" t="n">
         <v>1.1299</v>
@@ -2092,13 +2092,13 @@
         <v>0.6525</v>
       </c>
       <c r="S21" t="n">
-        <v>0.4161</v>
+        <v>0.5357</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8784</v>
+        <v>-0.5432</v>
       </c>
       <c r="U21" t="n">
-        <v>1.2946</v>
+        <v>1.0788</v>
       </c>
       <c r="V21" t="n">
         <v>-0.1745</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.661</v>
+        <v>-5.0483</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.726</v>
+        <v>-4.3907</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.9350000000000001</v>
+        <v>-0.6576</v>
       </c>
       <c r="G22" t="n">
         <v>-2.9537</v>
@@ -2170,13 +2170,13 @@
         <v>1.305</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.512</v>
+        <v>0.1006</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6165</v>
+        <v>-0.2812</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1044</v>
+        <v>0.3818</v>
       </c>
       <c r="V22" t="n">
         <v>-1.3252</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-7.1004</v>
+        <v>-5.5744</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.929</v>
+        <v>-4.5879</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.1714</v>
+        <v>-0.9865</v>
       </c>
       <c r="G23" t="n">
         <v>-3.7372</v>
@@ -2248,13 +2248,13 @@
         <v>1.5225</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4932</v>
+        <v>1.0329</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6609</v>
+        <v>0.6802</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1678</v>
+        <v>0.3527</v>
       </c>
       <c r="V23" t="n">
         <v>-1.13</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-9.598100000000001</v>
+        <v>-9.597899999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>-13.5621</v>
+        <v>-13.5622</v>
       </c>
       <c r="F24" t="n">
-        <v>3.964399999999999</v>
+        <v>3.9642</v>
       </c>
       <c r="G24" t="n">
         <v>-10.1679</v>
@@ -2299,10 +2299,10 @@
         <v>4.9922</v>
       </c>
       <c r="J24" t="n">
-        <v>1.109099999999999</v>
+        <v>1.1091</v>
       </c>
       <c r="K24" t="n">
-        <v>-3.8595</v>
+        <v>-3.859499999999999</v>
       </c>
       <c r="L24" t="n">
         <v>4.968700000000001</v>
@@ -2314,10 +2314,10 @@
         <v>-11.3012</v>
       </c>
       <c r="O24" t="n">
-        <v>0.02379999999999996</v>
+        <v>0.02379999999999985</v>
       </c>
       <c r="P24" t="n">
-        <v>-6.5253</v>
+        <v>-6.525300000000001</v>
       </c>
       <c r="Q24" t="n">
         <v>-20.6631</v>
@@ -2329,10 +2329,10 @@
         <v>9.745800000000001</v>
       </c>
       <c r="T24" t="n">
-        <v>1.6466</v>
+        <v>1.6465</v>
       </c>
       <c r="U24" t="n">
-        <v>8.099400000000001</v>
+        <v>8.099299999999999</v>
       </c>
       <c r="V24" t="n">
         <v>-2.650399999999999</v>
